--- a/terre-natale/tools/src/Terre Natale - Aides de jeu _ Castes.xlsx
+++ b/terre-natale/tools/src/Terre Natale - Aides de jeu _ Castes.xlsx
@@ -19,14 +19,41 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={20cbfdc3-5c73-4e21-a3ac-2524b35838cf}</author>
-    <author>tc={60adb1f7-13f3-46cc-b02a-a6d54fce8702}</author>
-    <author>tc={b4cea1f0-dea4-49ec-a369-d14b7c008795}</author>
-    <author>tc={bb357c44-27e9-4a1f-86a0-816c03b1b434}</author>
-    <author>tc={c21f7513-c191-4fa1-ac05-8052610b2699}</author>
+    <author>tc={0b64429b-7477-4641-bff4-cd944d927e39}</author>
+    <author>tc={3f71dd0b-c1c4-4e7c-b636-44aa96de889e}</author>
+    <author>tc={5f099a7d-a44c-45f1-9aaa-ffa84235666d}</author>
+    <author>tc={a3b09cd6-e4ca-44cf-8883-b137a6e2c935}</author>
+    <author>tc={a6a343ab-8468-485d-b27f-37855fbc9d65}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{20cbfdc3-5c73-4e21-a3ac-2524b35838cf}" ref="A189">
+    <comment authorId="0" xr:uid="{0b64429b-7477-4641-bff4-cd944d927e39}" ref="R168">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Ou bien ses actions passivement repousse/renverse ? ou conditions tel que confusion etc ?
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{3f71dd0b-c1c4-4e7c-b636-44aa96de889e}" ref="P117">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	A voir, ça pourrait affecter les alliés, mais +3 c'est beaucoup aussi pour un simple trait donc à modérer
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{5f099a7d-a44c-45f1-9aaa-ffa84235666d}" ref="A193">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	bricoleur magique
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{a3b09cd6-e4ca-44cf-8883-b137a6e2c935}" ref="A189">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -45,34 +72,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{60adb1f7-13f3-46cc-b02a-a6d54fce8702}" ref="P117">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	A voir, ça pourrait affecter les alliés, mais +3 c'est beaucoup aussi pour un simple trait donc à modérer
-</t>
-      </text>
-    </comment>
-    <comment authorId="2" xr:uid="{b4cea1f0-dea4-49ec-a369-d14b7c008795}" ref="R168">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Ou bien ses actions passivement repousse/renverse ? ou conditions tel que confusion etc ?
-</t>
-      </text>
-    </comment>
-    <comment authorId="3" xr:uid="{bb357c44-27e9-4a1f-86a0-816c03b1b434}" ref="A193">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	bricoleur magique
-</t>
-      </text>
-    </comment>
-    <comment authorId="4" xr:uid="{c21f7513-c191-4fa1-ac05-8052610b2699}" ref="P118">
+    <comment authorId="4" xr:uid="{a6a343ab-8468-485d-b27f-37855fbc9d65}" ref="P118">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -4186,8 +4186,8 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Alexandre J" id="{93d5f3c9-42c7-4e7c-acc8-582ec5750fbe}" providerId="google-sheets"/>
-  <x18tc:person displayName="Maximin Deschamps" id="{a5d6a935-10ed-4695-a295-cd5a4f1ab9e5}" providerId="google-sheets"/>
+  <x18tc:person displayName="Alexandre J" id="{64075eef-872d-4596-a6d5-37b3106943a9}" providerId="google-sheets"/>
+  <x18tc:person displayName="Maximin Deschamps" id="{2aea0dd2-ed57-4815-870c-920cda9df307}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -4387,33 +4387,33 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="R168" dT="2025-06-10T16:02:55.00" personId="{93d5f3c9-42c7-4e7c-acc8-582ec5750fbe}" id="{b4cea1f0-dea4-49ec-a369-d14b7c008795}" done="1">
+  <x18tc:threadedComment ref="R168" dT="2025-06-10T16:02:55.00" personId="{64075eef-872d-4596-a6d5-37b3106943a9}" id="{0b64429b-7477-4641-bff4-cd944d927e39}" done="1">
     <x18tc:text xml:space="preserve">Ou bien ses actions passivement repousse/renverse ? ou conditions tel que confusion etc ?</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="P118" dT="2025-06-05T15:43:14.00" personId="{93d5f3c9-42c7-4e7c-acc8-582ec5750fbe}" id="{c21f7513-c191-4fa1-ac05-8052610b2699}" done="0">
+  <x18tc:threadedComment ref="P118" dT="2025-06-05T15:43:14.00" personId="{64075eef-872d-4596-a6d5-37b3106943a9}" id="{a6a343ab-8468-485d-b27f-37855fbc9d65}" done="0">
     <x18tc:text xml:space="preserve">A voir, ça pourrait affecter les alliés, mais +3 c'est beaucoup aussi pour un simple trait donc à modérer</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A193" dT="2025-06-05T13:49:32.00" personId="{93d5f3c9-42c7-4e7c-acc8-582ec5750fbe}" id="{bb357c44-27e9-4a1f-86a0-816c03b1b434}" done="1">
+  <x18tc:threadedComment ref="A193" dT="2025-06-05T13:49:32.00" personId="{64075eef-872d-4596-a6d5-37b3106943a9}" id="{5f099a7d-a44c-45f1-9aaa-ffa84235666d}" done="1">
     <x18tc:text xml:space="preserve">bricoleur magique</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A189" dT="2025-06-05T09:51:15.00" personId="{a5d6a935-10ed-4695-a295-cd5a4f1ab9e5}" id="{20cbfdc3-5c73-4e21-a3ac-2524b35838cf}" done="1">
+  <x18tc:threadedComment ref="A189" dT="2025-06-05T09:51:15.00" personId="{2aea0dd2-ed57-4815-870c-920cda9df307}" id="{a3b09cd6-e4ca-44cf-8883-b137a6e2c935}" done="1">
     <x18tc:text xml:space="preserve">Vetomancien? (Veto = Interdiction en latin)</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A189" dT="2025-06-05T12:09:33.00" personId="{93d5f3c9-42c7-4e7c-acc8-582ec5750fbe}" id="{276da6ed-58e7-47d3-82ba-14d3ac7e3521}" parentId="{20cbfdc3-5c73-4e21-a3ac-2524b35838cf}">
+  <x18tc:threadedComment ref="A189" dT="2025-06-05T12:09:33.00" personId="{64075eef-872d-4596-a6d5-37b3106943a9}" id="{6c7e44cf-260e-4e7e-ad4d-cedbc0fc5c19}" parentId="{a3b09cd6-e4ca-44cf-8883-b137a6e2c935}">
     <x18tc:text xml:space="preserve">ça me fait surtout penser à vétérinaire lol
 mais je suis d'accord pour dire que Sourceleur est pas un terme très explicite non plus et qu'on peux trouver mieux
 quelque chose -mancien ça me va mais faudrait un truc un différent je pense</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A189" dT="2025-06-05T12:19:03.00" personId="{a5d6a935-10ed-4695-a295-cd5a4f1ab9e5}" id="{27ea9ff5-aefe-4545-a5e4-23063f9f77c9}" parentId="{20cbfdc3-5c73-4e21-a3ac-2524b35838cf}">
+  <x18tc:threadedComment ref="A189" dT="2025-06-05T12:19:03.00" personId="{2aea0dd2-ed57-4815-870c-920cda9df307}" id="{047bae52-b998-46a4-a7b2-0de858644034}" parentId="{a3b09cd6-e4ca-44cf-8883-b137a6e2c935}">
     <x18tc:text xml:space="preserve">negatomancien</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A189" dT="2025-06-05T12:37:11.00" personId="{93d5f3c9-42c7-4e7c-acc8-582ec5750fbe}" id="{228161d2-804e-43e9-921b-ae8114691a28}" parentId="{20cbfdc3-5c73-4e21-a3ac-2524b35838cf}">
+  <x18tc:threadedComment ref="A189" dT="2025-06-05T12:37:11.00" personId="{64075eef-872d-4596-a6d5-37b3106943a9}" id="{ef99dd5d-c908-441a-a4cb-ad7a1ac4d66d}" parentId="{a3b09cd6-e4ca-44cf-8883-b137a6e2c935}">
     <x18tc:text xml:space="preserve">Cleptomancien ?</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A189" dT="2025-06-10T12:49:34.00" personId="{93d5f3c9-42c7-4e7c-acc8-582ec5750fbe}" id="{6d1a8d4a-8fdd-49d6-a03d-6ce364809b34}" parentId="{20cbfdc3-5c73-4e21-a3ac-2524b35838cf}">
+  <x18tc:threadedComment ref="A189" dT="2025-06-10T12:49:34.00" personId="{64075eef-872d-4596-a6d5-37b3106943a9}" id="{fbaf3df2-1984-41e0-8a87-ecfd052d8697}" parentId="{a3b09cd6-e4ca-44cf-8883-b137a6e2c935}">
     <x18tc:text xml:space="preserve">J'aime bien Cleptomancien, ça sonne bien je trouve, je change le nom et on y reviendra si vraiment ça te plait pas lol</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="P117" dT="2025-06-05T15:43:09.00" personId="{93d5f3c9-42c7-4e7c-acc8-582ec5750fbe}" id="{60adb1f7-13f3-46cc-b02a-a6d54fce8702}" done="0">
+  <x18tc:threadedComment ref="P117" dT="2025-06-05T15:43:09.00" personId="{64075eef-872d-4596-a6d5-37b3106943a9}" id="{3f71dd0b-c1c4-4e7c-b636-44aa96de889e}" done="0">
     <x18tc:text xml:space="preserve">A voir, ça pourrait affecter les alliés, mais +3 c'est beaucoup aussi pour un simple trait donc à modérer</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>

--- a/terre-natale/tools/src/Terre Natale - Aides de jeu _ Castes.xlsx
+++ b/terre-natale/tools/src/Terre Natale - Aides de jeu _ Castes.xlsx
@@ -10,7 +10,7 @@
     <sheet state="visible" name="Infos" sheetId="5" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Castes!$A$1:$AG$1064</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Castes!$A$1:$AG$1065</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
@@ -19,14 +19,32 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={a2be1967-028b-4a31-8c4b-193694871330}</author>
-    <author>tc={af9b37a8-0006-4605-bdb9-0976702579c0}</author>
-    <author>tc={aff34b67-4918-4cf7-ae6d-547aeaa1f464}</author>
-    <author>tc={e30aab83-ed87-4c6e-9442-8541de9fb4fc}</author>
-    <author>tc={fe2b586c-4618-4745-b9bc-a008368e660e}</author>
+    <author>tc={0ae0aafb-ceea-42b2-8c20-11243de45f70}</author>
+    <author>tc={4048f974-19bd-4968-a82c-19f03c1bbd78}</author>
+    <author>tc={60cb9004-ccb4-41dc-b121-9eae7ae98eba}</author>
+    <author>tc={63259b4d-681f-49a2-a306-4e0b78c0e9dd}</author>
+    <author>tc={b19d41cd-1e9f-4816-ab33-651afcf6c301}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{a2be1967-028b-4a31-8c4b-193694871330}" ref="A189">
+    <comment authorId="0" xr:uid="{0ae0aafb-ceea-42b2-8c20-11243de45f70}" ref="P118">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	A voir, ça pourrait affecter les alliés, mais +3 c'est beaucoup aussi pour un simple trait donc à modérer
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{4048f974-19bd-4968-a82c-19f03c1bbd78}" ref="R168">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Ou bien ses actions passivement repousse/renverse ? ou conditions tel que confusion etc ?
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{60cb9004-ccb4-41dc-b121-9eae7ae98eba}" ref="A189">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -45,7 +63,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{af9b37a8-0006-4605-bdb9-0976702579c0}" ref="A193">
+    <comment authorId="3" xr:uid="{63259b4d-681f-49a2-a306-4e0b78c0e9dd}" ref="A193">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -54,7 +72,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{aff34b67-4918-4cf7-ae6d-547aeaa1f464}" ref="P118">
+    <comment authorId="4" xr:uid="{b19d41cd-1e9f-4816-ab33-651afcf6c301}" ref="P117">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -63,30 +81,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="3" xr:uid="{e30aab83-ed87-4c6e-9442-8541de9fb4fc}" ref="P117">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	A voir, ça pourrait affecter les alliés, mais +3 c'est beaucoup aussi pour un simple trait donc à modérer
-</t>
-      </text>
-    </comment>
-    <comment authorId="4" xr:uid="{fe2b586c-4618-4745-b9bc-a008368e660e}" ref="R168">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Ou bien ses actions passivement repousse/renverse ? ou conditions tel que confusion etc ?
-</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6478" uniqueCount="1702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6425" uniqueCount="1707">
   <si>
     <t>moti</t>
   </si>
@@ -4117,9 +4117,6 @@
     <t>En ACTL OU peux choisir deux atouts à la place OU bonus de 3</t>
   </si>
   <si>
-    <t>Arme de jet, Outils, Science</t>
-  </si>
-  <si>
     <t>Les artificiers font parler explosifs, grenades et charges préparées. Leur expertise transforme la destruction en outil précis, même quand elle reste bruyante.</t>
   </si>
   <si>
@@ -4952,6 +4949,24 @@
   </si>
   <si>
     <t>Les sourceleurs travaillent dans cercles de mages, lieux de pouvoir et expéditions arcanes où le mana lui-même est la ressource disputée.</t>
+  </si>
+  <si>
+    <t>Desperado</t>
+  </si>
+  <si>
+    <t>Fortune &amp; Sang-Froid</t>
+  </si>
+  <si>
+    <t>Concerne les tirs utilisant plus d'une munition à la fois (et profitant donc d'une cadence supérieure à 0)</t>
+  </si>
+  <si>
+    <t>Cadence des armes +1</t>
+  </si>
+  <si>
+    <t>Lorsque le personnage tir plusieurs munitions à la fois grâce à la cadence de son arme jusqu'à 1 munition toutes les 3 munitions sont sauvegardées (le tir produit les effets comme si la munition était tiré mais elle ne l'est pas vraiment, le maximum de munitions en plus lié à la cadence tiens compte de cette munition sauvegardé)</t>
+  </si>
+  <si>
+    <t>ACTS &amp; 3 PC – Desperado : La prochaine attaque du personnage, qui doit être réalisé lors du même tour, profite du bonus lié aux munitions tirées en plus sous la forme d'un bonus de maitrise</t>
   </si>
   <si>
     <t>Action</t>
@@ -5498,8 +5513,8 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Alexandre J" id="{2134a15c-ea12-44f4-ab6d-328f604ec82f}" providerId="google-sheets"/>
-  <x18tc:person displayName="Maximin Deschamps" id="{5bb4816c-25aa-452c-bc94-81a77bfd7328}" providerId="google-sheets"/>
+  <x18tc:person displayName="Alexandre J" id="{602e68d3-d088-45ca-b9bd-e0a4c75e9d4d}" providerId="google-sheets"/>
+  <x18tc:person displayName="Maximin Deschamps" id="{78849af8-c9db-440b-aec8-950abee7a80b}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -5699,33 +5714,33 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="R168" dT="2025-06-10T16:02:55.00" personId="{2134a15c-ea12-44f4-ab6d-328f604ec82f}" id="{fe2b586c-4618-4745-b9bc-a008368e660e}" done="1">
+  <x18tc:threadedComment ref="R168" dT="2025-06-10T16:02:55.00" personId="{602e68d3-d088-45ca-b9bd-e0a4c75e9d4d}" id="{4048f974-19bd-4968-a82c-19f03c1bbd78}" done="1">
     <x18tc:text xml:space="preserve">Ou bien ses actions passivement repousse/renverse ? ou conditions tel que confusion etc ?</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="P118" dT="2025-06-05T15:43:14.00" personId="{2134a15c-ea12-44f4-ab6d-328f604ec82f}" id="{aff34b67-4918-4cf7-ae6d-547aeaa1f464}" done="0">
+  <x18tc:threadedComment ref="P118" dT="2025-06-05T15:43:14.00" personId="{602e68d3-d088-45ca-b9bd-e0a4c75e9d4d}" id="{0ae0aafb-ceea-42b2-8c20-11243de45f70}" done="0">
     <x18tc:text xml:space="preserve">A voir, ça pourrait affecter les alliés, mais +3 c'est beaucoup aussi pour un simple trait donc à modérer</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A193" dT="2025-06-05T13:49:32.00" personId="{2134a15c-ea12-44f4-ab6d-328f604ec82f}" id="{af9b37a8-0006-4605-bdb9-0976702579c0}" done="1">
+  <x18tc:threadedComment ref="A193" dT="2025-06-05T13:49:32.00" personId="{602e68d3-d088-45ca-b9bd-e0a4c75e9d4d}" id="{63259b4d-681f-49a2-a306-4e0b78c0e9dd}" done="1">
     <x18tc:text xml:space="preserve">bricoleur magique</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A189" dT="2025-06-05T09:51:15.00" personId="{5bb4816c-25aa-452c-bc94-81a77bfd7328}" id="{a2be1967-028b-4a31-8c4b-193694871330}" done="1">
+  <x18tc:threadedComment ref="A189" dT="2025-06-05T09:51:15.00" personId="{78849af8-c9db-440b-aec8-950abee7a80b}" id="{60cb9004-ccb4-41dc-b121-9eae7ae98eba}" done="1">
     <x18tc:text xml:space="preserve">Vetomancien? (Veto = Interdiction en latin)</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A189" dT="2025-06-05T12:09:33.00" personId="{2134a15c-ea12-44f4-ab6d-328f604ec82f}" id="{7739823e-09c2-4b30-aed2-ad42dbe588be}" parentId="{a2be1967-028b-4a31-8c4b-193694871330}">
+  <x18tc:threadedComment ref="A189" dT="2025-06-05T12:09:33.00" personId="{602e68d3-d088-45ca-b9bd-e0a4c75e9d4d}" id="{4e83c4f4-0480-4cae-9083-d43bdb6dc1a2}" parentId="{60cb9004-ccb4-41dc-b121-9eae7ae98eba}">
     <x18tc:text xml:space="preserve">ça me fait surtout penser à vétérinaire lol
 mais je suis d'accord pour dire que Sourceleur est pas un terme très explicite non plus et qu'on peux trouver mieux
 quelque chose -mancien ça me va mais faudrait un truc un différent je pense</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A189" dT="2025-06-05T12:19:03.00" personId="{5bb4816c-25aa-452c-bc94-81a77bfd7328}" id="{ae21aee0-2397-4b36-9a89-ddf6febb6ce3}" parentId="{a2be1967-028b-4a31-8c4b-193694871330}">
+  <x18tc:threadedComment ref="A189" dT="2025-06-05T12:19:03.00" personId="{78849af8-c9db-440b-aec8-950abee7a80b}" id="{36f6eac6-3355-41d9-b709-7822ee45b05b}" parentId="{60cb9004-ccb4-41dc-b121-9eae7ae98eba}">
     <x18tc:text xml:space="preserve">negatomancien</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A189" dT="2025-06-05T12:37:11.00" personId="{2134a15c-ea12-44f4-ab6d-328f604ec82f}" id="{c9ad3ea0-57cc-4447-86fa-2be9a032f213}" parentId="{a2be1967-028b-4a31-8c4b-193694871330}">
+  <x18tc:threadedComment ref="A189" dT="2025-06-05T12:37:11.00" personId="{602e68d3-d088-45ca-b9bd-e0a4c75e9d4d}" id="{0a41068d-1306-473e-9ac5-58b6aa19a49b}" parentId="{60cb9004-ccb4-41dc-b121-9eae7ae98eba}">
     <x18tc:text xml:space="preserve">Cleptomancien ?</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A189" dT="2025-06-10T12:49:34.00" personId="{2134a15c-ea12-44f4-ab6d-328f604ec82f}" id="{a6c89d23-cc40-483f-b275-2f7c6a0e2937}" parentId="{a2be1967-028b-4a31-8c4b-193694871330}">
+  <x18tc:threadedComment ref="A189" dT="2025-06-10T12:49:34.00" personId="{602e68d3-d088-45ca-b9bd-e0a4c75e9d4d}" id="{9ac3280d-9ee9-4739-b477-0fb2673555aa}" parentId="{60cb9004-ccb4-41dc-b121-9eae7ae98eba}">
     <x18tc:text xml:space="preserve">J'aime bien Cleptomancien, ça sonne bien je trouve, je change le nom et on y reviendra si vraiment ça te plait pas lol</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="P117" dT="2025-06-05T15:43:09.00" personId="{2134a15c-ea12-44f4-ab6d-328f604ec82f}" id="{e30aab83-ed87-4c6e-9442-8541de9fb4fc}" done="0">
+  <x18tc:threadedComment ref="P117" dT="2025-06-05T15:43:09.00" personId="{602e68d3-d088-45ca-b9bd-e0a4c75e9d4d}" id="{b19d41cd-1e9f-4816-ab33-651afcf6c301}" done="0">
     <x18tc:text xml:space="preserve">A voir, ça pourrait affecter les alliés, mais +3 c'est beaucoup aussi pour un simple trait donc à modérer</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -13559,12 +13574,9 @@
         <v>205</v>
       </c>
       <c r="W127" s="15" t="s">
-        <v>205</v>
+        <v>1048</v>
       </c>
       <c r="X127" s="15" t="s">
-        <v>1048</v>
-      </c>
-      <c r="Y127" s="15" t="s">
         <v>1049</v>
       </c>
     </row>
@@ -13623,12 +13635,9 @@
         <v>1053</v>
       </c>
       <c r="W128" s="15" t="s">
-        <v>1022</v>
+        <v>1054</v>
       </c>
       <c r="X128" s="15" t="s">
-        <v>1054</v>
-      </c>
-      <c r="Y128" s="15" t="s">
         <v>1055</v>
       </c>
     </row>
@@ -13687,12 +13696,9 @@
         <v>1059</v>
       </c>
       <c r="W129" s="15" t="s">
-        <v>1022</v>
+        <v>1060</v>
       </c>
       <c r="X129" s="15" t="s">
-        <v>1060</v>
-      </c>
-      <c r="Y129" s="15" t="s">
         <v>1061</v>
       </c>
     </row>
@@ -13751,12 +13757,9 @@
         <v>1059</v>
       </c>
       <c r="W130" s="15" t="s">
-        <v>205</v>
+        <v>1066</v>
       </c>
       <c r="X130" s="15" t="s">
-        <v>1066</v>
-      </c>
-      <c r="Y130" s="15" t="s">
         <v>1067</v>
       </c>
     </row>
@@ -13813,12 +13816,9 @@
         <v>750</v>
       </c>
       <c r="W131" s="15" t="s">
-        <v>1022</v>
+        <v>1074</v>
       </c>
       <c r="X131" s="15" t="s">
-        <v>1074</v>
-      </c>
-      <c r="Y131" s="15" t="s">
         <v>1075</v>
       </c>
     </row>
@@ -13875,12 +13875,9 @@
         <v>1059</v>
       </c>
       <c r="W132" s="15" t="s">
-        <v>197</v>
+        <v>1081</v>
       </c>
       <c r="X132" s="15" t="s">
-        <v>1081</v>
-      </c>
-      <c r="Y132" s="15" t="s">
         <v>1082</v>
       </c>
     </row>
@@ -13935,12 +13932,9 @@
         <v>1089</v>
       </c>
       <c r="W133" s="15" t="s">
-        <v>205</v>
+        <v>1090</v>
       </c>
       <c r="X133" s="15" t="s">
-        <v>1090</v>
-      </c>
-      <c r="Y133" s="15" t="s">
         <v>1091</v>
       </c>
     </row>
@@ -13995,12 +13989,9 @@
         <v>1059</v>
       </c>
       <c r="W134" s="15" t="s">
-        <v>205</v>
+        <v>1097</v>
       </c>
       <c r="X134" s="15" t="s">
-        <v>1097</v>
-      </c>
-      <c r="Y134" s="15" t="s">
         <v>1098</v>
       </c>
     </row>
@@ -14059,12 +14050,9 @@
         <v>750</v>
       </c>
       <c r="W135" s="15" t="s">
-        <v>1053</v>
+        <v>1107</v>
       </c>
       <c r="X135" s="15" t="s">
-        <v>1107</v>
-      </c>
-      <c r="Y135" s="15" t="s">
         <v>1108</v>
       </c>
     </row>
@@ -14122,12 +14110,9 @@
         <v>1059</v>
       </c>
       <c r="W136" s="15" t="s">
-        <v>1059</v>
+        <v>1114</v>
       </c>
       <c r="X136" s="15" t="s">
-        <v>1114</v>
-      </c>
-      <c r="Y136" s="15" t="s">
         <v>1115</v>
       </c>
     </row>
@@ -14185,12 +14170,9 @@
         <v>1059</v>
       </c>
       <c r="W137" s="15" t="s">
-        <v>1059</v>
+        <v>1122</v>
       </c>
       <c r="X137" s="15" t="s">
-        <v>1122</v>
-      </c>
-      <c r="Y137" s="15" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -14248,12 +14230,9 @@
         <v>1059</v>
       </c>
       <c r="W138" s="15" t="s">
-        <v>750</v>
+        <v>1130</v>
       </c>
       <c r="X138" s="15" t="s">
-        <v>1130</v>
-      </c>
-      <c r="Y138" s="15" t="s">
         <v>1131</v>
       </c>
     </row>
@@ -14311,12 +14290,9 @@
         <v>1138</v>
       </c>
       <c r="W139" s="15" t="s">
-        <v>1059</v>
+        <v>1139</v>
       </c>
       <c r="X139" s="15" t="s">
-        <v>1139</v>
-      </c>
-      <c r="Y139" s="15" t="s">
         <v>1140</v>
       </c>
     </row>
@@ -14374,12 +14350,9 @@
         <v>213</v>
       </c>
       <c r="W140" s="15" t="s">
-        <v>1089</v>
+        <v>1147</v>
       </c>
       <c r="X140" s="15" t="s">
-        <v>1147</v>
-      </c>
-      <c r="Y140" s="15" t="s">
         <v>1148</v>
       </c>
     </row>
@@ -14437,12 +14410,9 @@
         <v>213</v>
       </c>
       <c r="W141" s="15" t="s">
-        <v>1059</v>
+        <v>1155</v>
       </c>
       <c r="X141" s="15" t="s">
-        <v>1155</v>
-      </c>
-      <c r="Y141" s="15" t="s">
         <v>1156</v>
       </c>
     </row>
@@ -14501,12 +14471,9 @@
         <v>50</v>
       </c>
       <c r="W142" s="15" t="s">
-        <v>750</v>
+        <v>1163</v>
       </c>
       <c r="X142" s="15" t="s">
-        <v>1163</v>
-      </c>
-      <c r="Y142" s="15" t="s">
         <v>1164</v>
       </c>
     </row>
@@ -14564,12 +14531,9 @@
         <v>71</v>
       </c>
       <c r="W143" s="15" t="s">
-        <v>1059</v>
+        <v>1172</v>
       </c>
       <c r="X143" s="15" t="s">
-        <v>1172</v>
-      </c>
-      <c r="Y143" s="15" t="s">
         <v>1173</v>
       </c>
     </row>
@@ -14627,12 +14591,9 @@
         <v>50</v>
       </c>
       <c r="W144" s="15" t="s">
-        <v>1059</v>
+        <v>1180</v>
       </c>
       <c r="X144" s="15" t="s">
-        <v>1180</v>
-      </c>
-      <c r="Y144" s="15" t="s">
         <v>1181</v>
       </c>
     </row>
@@ -14690,12 +14651,9 @@
         <v>197</v>
       </c>
       <c r="W145" s="15" t="s">
-        <v>1059</v>
+        <v>1188</v>
       </c>
       <c r="X145" s="15" t="s">
-        <v>1188</v>
-      </c>
-      <c r="Y145" s="15" t="s">
         <v>1189</v>
       </c>
     </row>
@@ -14753,12 +14711,9 @@
         <v>205</v>
       </c>
       <c r="W146" s="15" t="s">
-        <v>1138</v>
+        <v>1194</v>
       </c>
       <c r="X146" s="15" t="s">
-        <v>1194</v>
-      </c>
-      <c r="Y146" s="15" t="s">
         <v>1195</v>
       </c>
     </row>
@@ -14816,12 +14771,9 @@
         <v>786</v>
       </c>
       <c r="W147" s="15" t="s">
-        <v>1138</v>
+        <v>1202</v>
       </c>
       <c r="X147" s="15" t="s">
-        <v>1202</v>
-      </c>
-      <c r="Y147" s="15" t="s">
         <v>1203</v>
       </c>
     </row>
@@ -14880,12 +14832,9 @@
         <v>786</v>
       </c>
       <c r="W148" s="15" t="s">
-        <v>213</v>
+        <v>1210</v>
       </c>
       <c r="X148" s="15" t="s">
-        <v>1210</v>
-      </c>
-      <c r="Y148" s="15" t="s">
         <v>1211</v>
       </c>
     </row>
@@ -14944,12 +14893,9 @@
         <v>786</v>
       </c>
       <c r="W149" s="15" t="s">
-        <v>50</v>
+        <v>1220</v>
       </c>
       <c r="X149" s="15" t="s">
-        <v>1220</v>
-      </c>
-      <c r="Y149" s="15" t="s">
         <v>1221</v>
       </c>
     </row>
@@ -15007,12 +14953,9 @@
         <v>769</v>
       </c>
       <c r="W150" s="15" t="s">
-        <v>71</v>
+        <v>1228</v>
       </c>
       <c r="X150" s="15" t="s">
-        <v>1228</v>
-      </c>
-      <c r="Y150" s="15" t="s">
         <v>1229</v>
       </c>
     </row>
@@ -15070,12 +15013,9 @@
         <v>284</v>
       </c>
       <c r="W151" s="15" t="s">
-        <v>50</v>
+        <v>1237</v>
       </c>
       <c r="X151" s="15" t="s">
-        <v>1237</v>
-      </c>
-      <c r="Y151" s="15" t="s">
         <v>1238</v>
       </c>
     </row>
@@ -15133,12 +15073,9 @@
         <v>274</v>
       </c>
       <c r="W152" s="15" t="s">
-        <v>197</v>
+        <v>1246</v>
       </c>
       <c r="X152" s="15" t="s">
-        <v>1246</v>
-      </c>
-      <c r="Y152" s="15" t="s">
         <v>1247</v>
       </c>
     </row>
@@ -15196,12 +15133,9 @@
         <v>257</v>
       </c>
       <c r="W153" s="15" t="s">
-        <v>205</v>
+        <v>1254</v>
       </c>
       <c r="X153" s="15" t="s">
-        <v>1254</v>
-      </c>
-      <c r="Y153" s="15" t="s">
         <v>1255</v>
       </c>
     </row>
@@ -15260,12 +15194,9 @@
         <v>50</v>
       </c>
       <c r="W154" s="15" t="s">
-        <v>786</v>
+        <v>1262</v>
       </c>
       <c r="X154" s="15" t="s">
-        <v>1262</v>
-      </c>
-      <c r="Y154" s="15" t="s">
         <v>1263</v>
       </c>
     </row>
@@ -15324,12 +15255,9 @@
         <v>50</v>
       </c>
       <c r="W155" s="15" t="s">
-        <v>786</v>
+        <v>1270</v>
       </c>
       <c r="X155" s="15" t="s">
-        <v>1270</v>
-      </c>
-      <c r="Y155" s="15" t="s">
         <v>1271</v>
       </c>
     </row>
@@ -15388,12 +15316,9 @@
         <v>786</v>
       </c>
       <c r="W156" s="15" t="s">
-        <v>786</v>
+        <v>1278</v>
       </c>
       <c r="X156" s="15" t="s">
-        <v>1278</v>
-      </c>
-      <c r="Y156" s="15" t="s">
         <v>1279</v>
       </c>
     </row>
@@ -15452,12 +15377,9 @@
         <v>105</v>
       </c>
       <c r="W157" s="15" t="s">
-        <v>769</v>
+        <v>1286</v>
       </c>
       <c r="X157" s="15" t="s">
-        <v>1286</v>
-      </c>
-      <c r="Y157" s="15" t="s">
         <v>1287</v>
       </c>
     </row>
@@ -15515,12 +15437,9 @@
         <v>1294</v>
       </c>
       <c r="W158" s="15" t="s">
-        <v>284</v>
+        <v>1295</v>
       </c>
       <c r="X158" s="15" t="s">
-        <v>1295</v>
-      </c>
-      <c r="Y158" s="15" t="s">
         <v>1296</v>
       </c>
     </row>
@@ -15578,12 +15497,9 @@
         <v>257</v>
       </c>
       <c r="W159" s="15" t="s">
-        <v>274</v>
+        <v>1303</v>
       </c>
       <c r="X159" s="15" t="s">
-        <v>1303</v>
-      </c>
-      <c r="Y159" s="15" t="s">
         <v>1304</v>
       </c>
     </row>
@@ -15641,12 +15557,9 @@
         <v>50</v>
       </c>
       <c r="W160" s="15" t="s">
-        <v>257</v>
+        <v>1311</v>
       </c>
       <c r="X160" s="15" t="s">
-        <v>1311</v>
-      </c>
-      <c r="Y160" s="15" t="s">
         <v>1312</v>
       </c>
     </row>
@@ -15704,12 +15617,9 @@
         <v>205</v>
       </c>
       <c r="W161" s="15" t="s">
-        <v>50</v>
+        <v>1319</v>
       </c>
       <c r="X161" s="15" t="s">
-        <v>1319</v>
-      </c>
-      <c r="Y161" s="15" t="s">
         <v>1320</v>
       </c>
     </row>
@@ -15767,12 +15677,9 @@
         <v>944</v>
       </c>
       <c r="W162" s="15" t="s">
-        <v>50</v>
+        <v>1327</v>
       </c>
       <c r="X162" s="15" t="s">
-        <v>1327</v>
-      </c>
-      <c r="Y162" s="15" t="s">
         <v>1328</v>
       </c>
     </row>
@@ -15831,12 +15738,9 @@
         <v>71</v>
       </c>
       <c r="W163" s="15" t="s">
-        <v>786</v>
+        <v>1335</v>
       </c>
       <c r="X163" s="15" t="s">
-        <v>1335</v>
-      </c>
-      <c r="Y163" s="15" t="s">
         <v>1336</v>
       </c>
     </row>
@@ -15899,13 +15803,10 @@
       <c r="X164" s="15" t="s">
         <v>1344</v>
       </c>
-      <c r="Y164" s="15" t="s">
-        <v>1345</v>
-      </c>
     </row>
     <row r="165">
       <c r="A165" s="11" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="B165" s="12" t="s">
         <v>110</v>
@@ -15930,45 +15831,42 @@
         <v>224</v>
       </c>
       <c r="L165" s="35" t="s">
+        <v>1346</v>
+      </c>
+      <c r="M165" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N165" s="13" t="s">
         <v>1347</v>
       </c>
-      <c r="M165" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N165" s="13" t="s">
+      <c r="O165" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P165" s="13" t="s">
         <v>1348</v>
       </c>
-      <c r="O165" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P165" s="13" t="s">
+      <c r="Q165" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R165" s="13" t="s">
         <v>1349</v>
       </c>
-      <c r="Q165" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R165" s="13" t="s">
+      <c r="S165" s="13" t="s">
         <v>1350</v>
-      </c>
-      <c r="S165" s="13" t="s">
-        <v>1351</v>
       </c>
       <c r="V165" s="13" t="s">
         <v>205</v>
       </c>
       <c r="W165" s="15" t="s">
-        <v>50</v>
+        <v>1351</v>
       </c>
       <c r="X165" s="15" t="s">
         <v>1352</v>
       </c>
-      <c r="Y165" s="15" t="s">
-        <v>1353</v>
-      </c>
     </row>
     <row r="166">
       <c r="A166" s="11" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="B166" s="12" t="s">
         <v>110</v>
@@ -15999,39 +15897,36 @@
         <v>9</v>
       </c>
       <c r="N166" s="13" t="s">
+        <v>1354</v>
+      </c>
+      <c r="O166" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P166" s="13" t="s">
         <v>1355</v>
       </c>
-      <c r="O166" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P166" s="13" t="s">
+      <c r="Q166" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R166" s="13" t="s">
         <v>1356</v>
       </c>
-      <c r="Q166" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R166" s="13" t="s">
+      <c r="S166" s="13" t="s">
         <v>1357</v>
-      </c>
-      <c r="S166" s="13" t="s">
-        <v>1358</v>
       </c>
       <c r="V166" s="13" t="s">
         <v>50</v>
       </c>
       <c r="W166" s="15" t="s">
-        <v>105</v>
+        <v>1358</v>
       </c>
       <c r="X166" s="15" t="s">
         <v>1359</v>
       </c>
-      <c r="Y166" s="15" t="s">
-        <v>1360</v>
-      </c>
     </row>
     <row r="167">
       <c r="A167" s="11" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="B167" s="12" t="s">
         <v>110</v>
@@ -16057,45 +15952,42 @@
       </c>
       <c r="K167" s="14"/>
       <c r="L167" s="14" t="s">
+        <v>1361</v>
+      </c>
+      <c r="M167" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N167" s="13" t="s">
         <v>1362</v>
       </c>
-      <c r="M167" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N167" s="13" t="s">
+      <c r="O167" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P167" s="13" t="s">
         <v>1363</v>
       </c>
-      <c r="O167" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P167" s="13" t="s">
+      <c r="Q167" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R167" s="13" t="s">
         <v>1364</v>
       </c>
-      <c r="Q167" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R167" s="13" t="s">
+      <c r="S167" s="13" t="s">
         <v>1365</v>
-      </c>
-      <c r="S167" s="13" t="s">
-        <v>1366</v>
       </c>
       <c r="V167" s="13" t="s">
         <v>118</v>
       </c>
       <c r="W167" s="15" t="s">
-        <v>1294</v>
+        <v>1366</v>
       </c>
       <c r="X167" s="15" t="s">
         <v>1367</v>
       </c>
-      <c r="Y167" s="15" t="s">
-        <v>1368</v>
-      </c>
     </row>
     <row r="168">
       <c r="A168" s="11" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="B168" s="12" t="s">
         <v>110</v>
@@ -16120,7 +16012,7 @@
         <v>553</v>
       </c>
       <c r="L168" s="14" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="M168" s="13" t="s">
         <v>9</v>
@@ -16132,33 +16024,30 @@
         <v>9</v>
       </c>
       <c r="P168" s="13" t="s">
+        <v>1370</v>
+      </c>
+      <c r="Q168" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R168" s="13" t="s">
         <v>1371</v>
       </c>
-      <c r="Q168" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R168" s="13" t="s">
+      <c r="S168" s="13" t="s">
         <v>1372</v>
-      </c>
-      <c r="S168" s="13" t="s">
-        <v>1373</v>
       </c>
       <c r="V168" s="13" t="s">
         <v>205</v>
       </c>
       <c r="W168" s="15" t="s">
-        <v>257</v>
+        <v>1373</v>
       </c>
       <c r="X168" s="15" t="s">
         <v>1374</v>
       </c>
-      <c r="Y168" s="15" t="s">
-        <v>1375</v>
-      </c>
     </row>
     <row r="169">
       <c r="A169" s="11" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="B169" s="12" t="s">
         <v>110</v>
@@ -16167,7 +16056,7 @@
         <v>168</v>
       </c>
       <c r="D169" s="12" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="E169" s="13" t="s">
         <v>45</v>
@@ -16183,45 +16072,42 @@
         <v>479</v>
       </c>
       <c r="L169" s="14" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M169" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N169" s="13" t="s">
         <v>1378</v>
       </c>
-      <c r="M169" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N169" s="13" t="s">
+      <c r="O169" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P169" s="13" t="s">
         <v>1379</v>
       </c>
-      <c r="O169" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P169" s="13" t="s">
+      <c r="Q169" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R169" s="13" t="s">
         <v>1380</v>
       </c>
-      <c r="Q169" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R169" s="13" t="s">
+      <c r="S169" s="13" t="s">
         <v>1381</v>
-      </c>
-      <c r="S169" s="13" t="s">
-        <v>1382</v>
       </c>
       <c r="V169" s="13" t="s">
         <v>71</v>
       </c>
       <c r="W169" s="15" t="s">
-        <v>50</v>
+        <v>1382</v>
       </c>
       <c r="X169" s="15" t="s">
         <v>1383</v>
       </c>
-      <c r="Y169" s="15" t="s">
-        <v>1384</v>
-      </c>
     </row>
     <row r="170">
       <c r="A170" s="11" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="B170" s="12" t="s">
         <v>110</v>
@@ -16230,7 +16116,7 @@
         <v>179</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="E170" s="13" t="s">
         <v>45</v>
@@ -16246,45 +16132,42 @@
         <v>224</v>
       </c>
       <c r="L170" s="14" t="s">
+        <v>1385</v>
+      </c>
+      <c r="M170" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N170" s="13" t="s">
         <v>1386</v>
       </c>
-      <c r="M170" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N170" s="13" t="s">
+      <c r="O170" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P170" s="13" t="s">
         <v>1387</v>
       </c>
-      <c r="O170" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P170" s="13" t="s">
+      <c r="Q170" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R170" s="13" t="s">
         <v>1388</v>
       </c>
-      <c r="Q170" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R170" s="13" t="s">
+      <c r="S170" s="13" t="s">
         <v>1389</v>
-      </c>
-      <c r="S170" s="13" t="s">
-        <v>1390</v>
       </c>
       <c r="V170" s="14" t="s">
         <v>743</v>
       </c>
       <c r="W170" s="15" t="s">
-        <v>205</v>
+        <v>1390</v>
       </c>
       <c r="X170" s="15" t="s">
         <v>1391</v>
       </c>
-      <c r="Y170" s="15" t="s">
-        <v>1392</v>
-      </c>
     </row>
     <row r="171">
       <c r="A171" s="11" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B171" s="12" t="s">
         <v>110</v>
@@ -16309,45 +16192,42 @@
         <v>217</v>
       </c>
       <c r="L171" s="14" t="s">
+        <v>1393</v>
+      </c>
+      <c r="M171" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N171" s="13" t="s">
         <v>1394</v>
       </c>
-      <c r="M171" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N171" s="13" t="s">
+      <c r="O171" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P171" s="13" t="s">
         <v>1395</v>
       </c>
-      <c r="O171" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P171" s="13" t="s">
+      <c r="Q171" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R171" s="13" t="s">
         <v>1396</v>
       </c>
-      <c r="Q171" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R171" s="13" t="s">
+      <c r="S171" s="13" t="s">
         <v>1397</v>
-      </c>
-      <c r="S171" s="13" t="s">
-        <v>1398</v>
       </c>
       <c r="V171" s="13" t="s">
         <v>205</v>
       </c>
       <c r="W171" s="15" t="s">
-        <v>944</v>
+        <v>1398</v>
       </c>
       <c r="X171" s="15" t="s">
         <v>1399</v>
       </c>
-      <c r="Y171" s="15" t="s">
-        <v>1400</v>
-      </c>
     </row>
     <row r="172">
       <c r="A172" s="11" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B172" s="12" t="s">
         <v>110</v>
@@ -16372,45 +16252,42 @@
         <v>158</v>
       </c>
       <c r="L172" s="35" t="s">
+        <v>1401</v>
+      </c>
+      <c r="M172" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N172" s="13" t="s">
         <v>1402</v>
       </c>
-      <c r="M172" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N172" s="13" t="s">
+      <c r="O172" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P172" s="13" t="s">
         <v>1403</v>
       </c>
-      <c r="O172" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P172" s="13" t="s">
+      <c r="Q172" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R172" s="13" t="s">
         <v>1404</v>
       </c>
-      <c r="Q172" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R172" s="13" t="s">
+      <c r="S172" s="13" t="s">
         <v>1405</v>
-      </c>
-      <c r="S172" s="13" t="s">
-        <v>1406</v>
       </c>
       <c r="V172" s="13" t="s">
         <v>197</v>
       </c>
       <c r="W172" s="15" t="s">
-        <v>71</v>
+        <v>1406</v>
       </c>
       <c r="X172" s="15" t="s">
         <v>1407</v>
       </c>
-      <c r="Y172" s="15" t="s">
-        <v>1408</v>
-      </c>
     </row>
     <row r="173">
       <c r="A173" s="11" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B173" s="12" t="s">
         <v>110</v>
@@ -16435,42 +16312,39 @@
         <v>158</v>
       </c>
       <c r="L173" s="14" t="s">
+        <v>1409</v>
+      </c>
+      <c r="N173" s="13" t="s">
         <v>1410</v>
       </c>
-      <c r="N173" s="13" t="s">
+      <c r="O173" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P173" s="13" t="s">
         <v>1411</v>
       </c>
-      <c r="O173" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P173" s="13" t="s">
+      <c r="Q173" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R173" s="13" t="s">
         <v>1412</v>
       </c>
-      <c r="Q173" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R173" s="13" t="s">
+      <c r="S173" s="13" t="s">
         <v>1413</v>
-      </c>
-      <c r="S173" s="13" t="s">
-        <v>1414</v>
       </c>
       <c r="V173" s="13" t="s">
         <v>205</v>
       </c>
       <c r="W173" s="15" t="s">
-        <v>50</v>
+        <v>1414</v>
       </c>
       <c r="X173" s="15" t="s">
         <v>1415</v>
       </c>
-      <c r="Y173" s="15" t="s">
-        <v>1416</v>
-      </c>
     </row>
     <row r="174">
       <c r="A174" s="11" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B174" s="12" t="s">
         <v>110</v>
@@ -16479,7 +16353,7 @@
         <v>167</v>
       </c>
       <c r="D174" s="12" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="E174" s="13" t="s">
         <v>45</v>
@@ -16495,45 +16369,42 @@
         <v>479</v>
       </c>
       <c r="L174" s="13" t="s">
+        <v>1418</v>
+      </c>
+      <c r="M174" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N174" s="13" t="s">
         <v>1419</v>
       </c>
-      <c r="M174" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N174" s="13" t="s">
+      <c r="O174" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P174" s="13" t="s">
         <v>1420</v>
       </c>
-      <c r="O174" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P174" s="13" t="s">
+      <c r="Q174" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R174" s="13" t="s">
         <v>1421</v>
       </c>
-      <c r="Q174" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R174" s="13" t="s">
+      <c r="S174" s="13" t="s">
         <v>1422</v>
-      </c>
-      <c r="S174" s="13" t="s">
-        <v>1423</v>
       </c>
       <c r="V174" s="13" t="s">
         <v>205</v>
       </c>
       <c r="W174" s="15" t="s">
-        <v>50</v>
+        <v>1423</v>
       </c>
       <c r="X174" s="15" t="s">
         <v>1424</v>
       </c>
-      <c r="Y174" s="15" t="s">
-        <v>1425</v>
-      </c>
     </row>
     <row r="175">
       <c r="A175" s="11" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B175" s="12" t="s">
         <v>110</v>
@@ -16558,45 +16429,42 @@
         <v>344</v>
       </c>
       <c r="L175" s="35" t="s">
+        <v>1426</v>
+      </c>
+      <c r="M175" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N175" s="13" t="s">
         <v>1427</v>
       </c>
-      <c r="M175" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N175" s="13" t="s">
+      <c r="O175" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P175" s="13" t="s">
         <v>1428</v>
       </c>
-      <c r="O175" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P175" s="13" t="s">
+      <c r="Q175" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R175" s="13" t="s">
         <v>1429</v>
-      </c>
-      <c r="Q175" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R175" s="13" t="s">
-        <v>1430</v>
       </c>
       <c r="S175" s="13" t="s">
         <v>893</v>
       </c>
       <c r="V175" s="13" t="s">
+        <v>1430</v>
+      </c>
+      <c r="W175" s="15" t="s">
         <v>1431</v>
-      </c>
-      <c r="W175" s="15" t="s">
-        <v>153</v>
       </c>
       <c r="X175" s="15" t="s">
         <v>1432</v>
       </c>
-      <c r="Y175" s="15" t="s">
-        <v>1433</v>
-      </c>
     </row>
     <row r="176">
       <c r="A176" s="11" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B176" s="12" t="s">
         <v>110</v>
@@ -16621,45 +16489,42 @@
         <v>621</v>
       </c>
       <c r="L176" s="35" t="s">
+        <v>1434</v>
+      </c>
+      <c r="M176" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N176" s="13" t="s">
         <v>1435</v>
       </c>
-      <c r="M176" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N176" s="13" t="s">
+      <c r="O176" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P176" s="13" t="s">
         <v>1436</v>
       </c>
-      <c r="O176" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P176" s="13" t="s">
+      <c r="Q176" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R176" s="13" t="s">
         <v>1437</v>
-      </c>
-      <c r="Q176" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R176" s="13" t="s">
-        <v>1438</v>
       </c>
       <c r="S176" s="13" t="s">
         <v>893</v>
       </c>
       <c r="V176" s="13" t="s">
+        <v>1438</v>
+      </c>
+      <c r="W176" s="15" t="s">
         <v>1439</v>
-      </c>
-      <c r="W176" s="15" t="s">
-        <v>205</v>
       </c>
       <c r="X176" s="15" t="s">
         <v>1440</v>
       </c>
-      <c r="Y176" s="15" t="s">
-        <v>1441</v>
-      </c>
     </row>
     <row r="177">
       <c r="A177" s="11" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B177" s="12" t="s">
         <v>110</v>
@@ -16684,25 +16549,25 @@
         <v>437</v>
       </c>
       <c r="L177" s="35" t="s">
+        <v>1442</v>
+      </c>
+      <c r="M177" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N177" s="13" t="s">
         <v>1443</v>
       </c>
-      <c r="M177" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N177" s="13" t="s">
+      <c r="O177" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P177" s="13" t="s">
         <v>1444</v>
       </c>
-      <c r="O177" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P177" s="13" t="s">
+      <c r="Q177" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R177" s="13" t="s">
         <v>1445</v>
-      </c>
-      <c r="Q177" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R177" s="13" t="s">
-        <v>1446</v>
       </c>
       <c r="S177" s="13" t="s">
         <v>998</v>
@@ -16711,18 +16576,15 @@
         <v>71</v>
       </c>
       <c r="W177" s="15" t="s">
-        <v>118</v>
+        <v>1446</v>
       </c>
       <c r="X177" s="15" t="s">
         <v>1447</v>
       </c>
-      <c r="Y177" s="15" t="s">
-        <v>1448</v>
-      </c>
     </row>
     <row r="178">
       <c r="A178" s="11" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B178" s="12" t="s">
         <v>110</v>
@@ -16731,7 +16593,7 @@
         <v>179</v>
       </c>
       <c r="D178" s="12" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="E178" s="13" t="s">
         <v>45</v>
@@ -16747,45 +16609,42 @@
         <v>344</v>
       </c>
       <c r="L178" s="35" t="s">
+        <v>1450</v>
+      </c>
+      <c r="M178" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N178" s="13" t="s">
         <v>1451</v>
       </c>
-      <c r="M178" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N178" s="13" t="s">
+      <c r="O178" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P178" s="13" t="s">
         <v>1452</v>
       </c>
-      <c r="O178" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P178" s="13" t="s">
+      <c r="Q178" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R178" s="13" t="s">
         <v>1453</v>
       </c>
-      <c r="Q178" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R178" s="13" t="s">
+      <c r="S178" s="13" t="s">
         <v>1454</v>
-      </c>
-      <c r="S178" s="13" t="s">
-        <v>1455</v>
       </c>
       <c r="V178" s="14" t="s">
         <v>50</v>
       </c>
       <c r="W178" s="15" t="s">
-        <v>1022</v>
+        <v>1455</v>
       </c>
       <c r="X178" s="15" t="s">
         <v>1456</v>
       </c>
-      <c r="Y178" s="15" t="s">
-        <v>1457</v>
-      </c>
     </row>
     <row r="179">
       <c r="A179" s="11" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B179" s="12" t="s">
         <v>110</v>
@@ -16810,45 +16669,42 @@
         <v>322</v>
       </c>
       <c r="L179" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="M179" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N179" s="13" t="s">
         <v>1459</v>
       </c>
-      <c r="M179" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N179" s="13" t="s">
+      <c r="O179" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P179" s="13" t="s">
         <v>1460</v>
       </c>
-      <c r="O179" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P179" s="13" t="s">
+      <c r="Q179" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R179" s="13" t="s">
         <v>1461</v>
       </c>
-      <c r="Q179" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R179" s="13" t="s">
+      <c r="S179" s="13" t="s">
         <v>1462</v>
-      </c>
-      <c r="S179" s="13" t="s">
-        <v>1463</v>
       </c>
       <c r="V179" s="13" t="s">
         <v>71</v>
       </c>
       <c r="W179" s="15" t="s">
-        <v>71</v>
+        <v>1463</v>
       </c>
       <c r="X179" s="15" t="s">
         <v>1464</v>
       </c>
-      <c r="Y179" s="15" t="s">
-        <v>1465</v>
-      </c>
     </row>
     <row r="180">
       <c r="A180" s="11" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B180" s="12" t="s">
         <v>110</v>
@@ -16873,42 +16729,39 @@
         <v>217</v>
       </c>
       <c r="L180" s="35" t="s">
+        <v>1466</v>
+      </c>
+      <c r="N180" s="13" t="s">
         <v>1467</v>
       </c>
-      <c r="N180" s="13" t="s">
+      <c r="O180" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P180" s="13" t="s">
         <v>1468</v>
       </c>
-      <c r="O180" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P180" s="13" t="s">
+      <c r="Q180" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R180" s="13" t="s">
         <v>1469</v>
       </c>
-      <c r="Q180" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R180" s="13" t="s">
+      <c r="S180" s="13" t="s">
         <v>1470</v>
-      </c>
-      <c r="S180" s="13" t="s">
-        <v>1471</v>
       </c>
       <c r="V180" s="13" t="s">
         <v>205</v>
       </c>
       <c r="W180" s="15" t="s">
-        <v>743</v>
+        <v>1471</v>
       </c>
       <c r="X180" s="15" t="s">
         <v>1472</v>
       </c>
-      <c r="Y180" s="15" t="s">
-        <v>1473</v>
-      </c>
     </row>
     <row r="181">
       <c r="A181" s="11" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B181" s="12" t="s">
         <v>110</v>
@@ -16933,45 +16786,42 @@
         <v>217</v>
       </c>
       <c r="L181" s="35" t="s">
+        <v>1474</v>
+      </c>
+      <c r="M181" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N181" s="13" t="s">
         <v>1475</v>
       </c>
-      <c r="M181" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N181" s="13" t="s">
+      <c r="O181" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P181" s="13" t="s">
         <v>1476</v>
       </c>
-      <c r="O181" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P181" s="13" t="s">
+      <c r="Q181" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R181" s="13" t="s">
         <v>1477</v>
       </c>
-      <c r="Q181" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R181" s="13" t="s">
+      <c r="S181" s="13" t="s">
         <v>1478</v>
-      </c>
-      <c r="S181" s="13" t="s">
-        <v>1479</v>
       </c>
       <c r="V181" s="13" t="s">
         <v>205</v>
       </c>
       <c r="W181" s="15" t="s">
-        <v>205</v>
+        <v>1479</v>
       </c>
       <c r="X181" s="15" t="s">
         <v>1480</v>
       </c>
-      <c r="Y181" s="15" t="s">
-        <v>1481</v>
-      </c>
     </row>
     <row r="182">
       <c r="A182" s="11" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B182" s="12" t="s">
         <v>110</v>
@@ -16996,45 +16846,42 @@
         <v>147</v>
       </c>
       <c r="L182" s="35" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M182" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N182" s="13" t="s">
         <v>1483</v>
       </c>
-      <c r="M182" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N182" s="13" t="s">
+      <c r="O182" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P182" s="13" t="s">
         <v>1484</v>
       </c>
-      <c r="O182" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P182" s="13" t="s">
+      <c r="Q182" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R182" s="13" t="s">
         <v>1485</v>
       </c>
-      <c r="Q182" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R182" s="13" t="s">
+      <c r="S182" s="13" t="s">
         <v>1486</v>
-      </c>
-      <c r="S182" s="13" t="s">
-        <v>1487</v>
       </c>
       <c r="V182" s="13" t="s">
         <v>205</v>
       </c>
       <c r="W182" s="15" t="s">
-        <v>197</v>
+        <v>1487</v>
       </c>
       <c r="X182" s="15" t="s">
         <v>1488</v>
       </c>
-      <c r="Y182" s="15" t="s">
-        <v>1489</v>
-      </c>
     </row>
     <row r="183">
       <c r="A183" s="11" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B183" s="12" t="s">
         <v>110</v>
@@ -17056,48 +16903,45 @@
         <v>57</v>
       </c>
       <c r="J183" s="13" t="s">
+        <v>1490</v>
+      </c>
+      <c r="L183" s="35" t="s">
         <v>1491</v>
       </c>
-      <c r="L183" s="35" t="s">
+      <c r="M183" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N183" s="13" t="s">
         <v>1492</v>
       </c>
-      <c r="M183" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N183" s="13" t="s">
+      <c r="O183" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P183" s="13" t="s">
         <v>1493</v>
       </c>
-      <c r="O183" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P183" s="13" t="s">
+      <c r="Q183" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R183" s="13" t="s">
         <v>1494</v>
-      </c>
-      <c r="Q183" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R183" s="13" t="s">
-        <v>1495</v>
       </c>
       <c r="S183" s="13" t="s">
         <v>1014</v>
       </c>
       <c r="V183" s="13" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="W183" s="15" t="s">
-        <v>1431</v>
+        <v>1495</v>
       </c>
       <c r="X183" s="15" t="s">
         <v>1496</v>
       </c>
-      <c r="Y183" s="15" t="s">
-        <v>1497</v>
-      </c>
     </row>
     <row r="184">
       <c r="A184" s="11" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="B184" s="12" t="s">
         <v>110</v>
@@ -17106,7 +16950,7 @@
         <v>179</v>
       </c>
       <c r="D184" s="12" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="E184" s="13" t="s">
         <v>36</v>
@@ -17122,45 +16966,42 @@
         <v>1070</v>
       </c>
       <c r="L184" s="13" t="s">
+        <v>1499</v>
+      </c>
+      <c r="M184" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N184" s="13" t="s">
         <v>1500</v>
       </c>
-      <c r="M184" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N184" s="13" t="s">
+      <c r="O184" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P184" s="13" t="s">
         <v>1501</v>
       </c>
-      <c r="O184" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P184" s="13" t="s">
+      <c r="Q184" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R184" s="13" t="s">
         <v>1502</v>
-      </c>
-      <c r="Q184" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R184" s="13" t="s">
-        <v>1503</v>
       </c>
       <c r="S184" s="13" t="s">
         <v>1014</v>
       </c>
       <c r="V184" s="13" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="W184" s="15" t="s">
-        <v>1439</v>
+        <v>1503</v>
       </c>
       <c r="X184" s="15" t="s">
         <v>1504</v>
       </c>
-      <c r="Y184" s="15" t="s">
-        <v>1505</v>
-      </c>
     </row>
     <row r="185">
       <c r="A185" s="11" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="B185" s="12" t="s">
         <v>110</v>
@@ -17185,45 +17026,42 @@
         <v>553</v>
       </c>
       <c r="L185" s="35" t="s">
+        <v>1506</v>
+      </c>
+      <c r="M185" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N185" s="13" t="s">
         <v>1507</v>
       </c>
-      <c r="M185" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N185" s="13" t="s">
+      <c r="O185" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P185" s="13" t="s">
         <v>1508</v>
       </c>
-      <c r="O185" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P185" s="13" t="s">
+      <c r="Q185" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R185" s="13" t="s">
         <v>1509</v>
       </c>
-      <c r="Q185" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R185" s="13" t="s">
+      <c r="S185" s="13" t="s">
         <v>1510</v>
-      </c>
-      <c r="S185" s="13" t="s">
-        <v>1511</v>
       </c>
       <c r="V185" s="13" t="s">
         <v>71</v>
       </c>
       <c r="W185" s="15" t="s">
-        <v>71</v>
+        <v>1511</v>
       </c>
       <c r="X185" s="15" t="s">
         <v>1512</v>
       </c>
-      <c r="Y185" s="15" t="s">
-        <v>1513</v>
-      </c>
     </row>
     <row r="186">
       <c r="A186" s="11" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="B186" s="12" t="s">
         <v>110</v>
@@ -17248,45 +17086,42 @@
         <v>201</v>
       </c>
       <c r="L186" s="35" t="s">
+        <v>1514</v>
+      </c>
+      <c r="M186" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N186" s="13" t="s">
         <v>1515</v>
       </c>
-      <c r="M186" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N186" s="13" t="s">
+      <c r="O186" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P186" s="13" t="s">
         <v>1516</v>
       </c>
-      <c r="O186" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P186" s="13" t="s">
+      <c r="Q186" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R186" s="13" t="s">
         <v>1517</v>
       </c>
-      <c r="Q186" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R186" s="13" t="s">
+      <c r="S186" s="13" t="s">
         <v>1518</v>
-      </c>
-      <c r="S186" s="13" t="s">
-        <v>1519</v>
       </c>
       <c r="V186" s="13" t="s">
         <v>50</v>
       </c>
       <c r="W186" s="15" t="s">
-        <v>50</v>
+        <v>1519</v>
       </c>
       <c r="X186" s="15" t="s">
         <v>1520</v>
       </c>
-      <c r="Y186" s="15" t="s">
-        <v>1521</v>
-      </c>
     </row>
     <row r="187">
       <c r="A187" s="11" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B187" s="12" t="s">
         <v>110</v>
@@ -17311,45 +17146,42 @@
       </c>
       <c r="K187" s="48"/>
       <c r="L187" s="35" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="M187" s="13" t="s">
         <v>9</v>
       </c>
       <c r="N187" s="13" t="s">
+        <v>1522</v>
+      </c>
+      <c r="O187" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P187" s="13" t="s">
         <v>1523</v>
       </c>
-      <c r="O187" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P187" s="13" t="s">
+      <c r="Q187" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R187" s="13" t="s">
         <v>1524</v>
       </c>
-      <c r="Q187" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R187" s="13" t="s">
+      <c r="S187" s="13" t="s">
         <v>1525</v>
-      </c>
-      <c r="S187" s="13" t="s">
-        <v>1526</v>
       </c>
       <c r="V187" s="13" t="s">
         <v>71</v>
       </c>
       <c r="W187" s="15" t="s">
-        <v>71</v>
+        <v>1526</v>
       </c>
       <c r="X187" s="15" t="s">
         <v>1527</v>
       </c>
-      <c r="Y187" s="15" t="s">
-        <v>1528</v>
-      </c>
     </row>
     <row r="188">
       <c r="A188" s="11" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B188" s="12" t="s">
         <v>110</v>
@@ -17374,42 +17206,39 @@
       </c>
       <c r="K188" s="48"/>
       <c r="L188" s="13" t="s">
+        <v>1529</v>
+      </c>
+      <c r="N188" s="13" t="s">
         <v>1530</v>
       </c>
-      <c r="N188" s="13" t="s">
+      <c r="O188" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P188" s="13" t="s">
         <v>1531</v>
       </c>
-      <c r="O188" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P188" s="13" t="s">
+      <c r="Q188" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R188" s="13" t="s">
         <v>1532</v>
       </c>
-      <c r="Q188" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R188" s="13" t="s">
+      <c r="S188" s="13" t="s">
         <v>1533</v>
-      </c>
-      <c r="S188" s="13" t="s">
-        <v>1534</v>
       </c>
       <c r="V188" s="13" t="s">
         <v>205</v>
       </c>
       <c r="W188" s="15" t="s">
-        <v>205</v>
+        <v>1534</v>
       </c>
       <c r="X188" s="15" t="s">
         <v>1535</v>
       </c>
-      <c r="Y188" s="15" t="s">
-        <v>1536</v>
-      </c>
     </row>
     <row r="189">
       <c r="A189" s="11" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B189" s="12" t="s">
         <v>110</v>
@@ -17434,31 +17263,31 @@
         <v>191</v>
       </c>
       <c r="L189" s="35" t="s">
+        <v>1537</v>
+      </c>
+      <c r="M189" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N189" s="13" t="s">
         <v>1538</v>
       </c>
-      <c r="M189" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N189" s="13" t="s">
+      <c r="O189" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P189" s="13" t="s">
         <v>1539</v>
       </c>
-      <c r="O189" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P189" s="13" t="s">
+      <c r="Q189" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R189" s="13" t="s">
         <v>1540</v>
       </c>
-      <c r="Q189" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R189" s="13" t="s">
+      <c r="S189" s="13" t="s">
+        <v>1533</v>
+      </c>
+      <c r="V189" s="13" t="s">
         <v>1541</v>
-      </c>
-      <c r="S189" s="13" t="s">
-        <v>1534</v>
-      </c>
-      <c r="V189" s="13" t="s">
-        <v>1542</v>
       </c>
       <c r="W189" s="15" t="s">
         <v>1542</v>
@@ -17466,13 +17295,10 @@
       <c r="X189" s="15" t="s">
         <v>1543</v>
       </c>
-      <c r="Y189" s="15" t="s">
-        <v>1544</v>
-      </c>
     </row>
     <row r="190">
       <c r="A190" s="11" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="B190" s="12" t="s">
         <v>110</v>
@@ -17490,7 +17316,7 @@
         <v>23</v>
       </c>
       <c r="H190" s="12" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="I190" s="13" t="s">
         <v>124</v>
@@ -17499,48 +17325,45 @@
         <v>1231</v>
       </c>
       <c r="L190" s="35" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M190" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N190" s="13" t="s">
         <v>1547</v>
       </c>
-      <c r="M190" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N190" s="13" t="s">
+      <c r="O190" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P190" s="13" t="s">
         <v>1548</v>
       </c>
-      <c r="O190" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P190" s="13" t="s">
+      <c r="Q190" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R190" s="13" t="s">
         <v>1549</v>
-      </c>
-      <c r="Q190" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R190" s="13" t="s">
-        <v>1550</v>
       </c>
       <c r="S190" s="13" t="s">
         <v>893</v>
       </c>
       <c r="U190" s="13" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="V190" s="13" t="s">
         <v>591</v>
       </c>
       <c r="W190" s="15" t="s">
-        <v>591</v>
+        <v>1551</v>
       </c>
       <c r="X190" s="15" t="s">
         <v>1552</v>
       </c>
-      <c r="Y190" s="15" t="s">
-        <v>1553</v>
-      </c>
     </row>
     <row r="191">
       <c r="A191" s="11" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B191" s="12" t="s">
         <v>110</v>
@@ -17558,7 +17381,7 @@
         <v>190</v>
       </c>
       <c r="H191" s="12" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="I191" s="13" t="s">
         <v>57</v>
@@ -17567,45 +17390,42 @@
         <v>217</v>
       </c>
       <c r="L191" s="49" t="s">
+        <v>1555</v>
+      </c>
+      <c r="M191" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N191" s="13" t="s">
         <v>1556</v>
       </c>
-      <c r="M191" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N191" s="13" t="s">
+      <c r="O191" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P191" s="13" t="s">
         <v>1557</v>
       </c>
-      <c r="O191" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P191" s="13" t="s">
+      <c r="Q191" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R191" s="13" t="s">
         <v>1558</v>
       </c>
-      <c r="Q191" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R191" s="13" t="s">
+      <c r="S191" s="13" t="s">
         <v>1559</v>
-      </c>
-      <c r="S191" s="13" t="s">
-        <v>1560</v>
       </c>
       <c r="V191" s="13" t="s">
         <v>197</v>
       </c>
       <c r="W191" s="15" t="s">
-        <v>197</v>
+        <v>1560</v>
       </c>
       <c r="X191" s="15" t="s">
         <v>1561</v>
       </c>
-      <c r="Y191" s="15" t="s">
-        <v>1562</v>
-      </c>
     </row>
     <row r="192">
       <c r="A192" s="11" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B192" s="12" t="s">
         <v>110</v>
@@ -17630,45 +17450,42 @@
         <v>170</v>
       </c>
       <c r="L192" s="35" t="s">
+        <v>1563</v>
+      </c>
+      <c r="M192" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N192" s="13" t="s">
         <v>1564</v>
       </c>
-      <c r="M192" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N192" s="13" t="s">
+      <c r="O192" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P192" s="35" t="s">
         <v>1565</v>
       </c>
-      <c r="O192" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P192" s="35" t="s">
+      <c r="Q192" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R192" s="13" t="s">
         <v>1566</v>
       </c>
-      <c r="Q192" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R192" s="13" t="s">
+      <c r="S192" s="13" t="s">
         <v>1567</v>
-      </c>
-      <c r="S192" s="13" t="s">
-        <v>1568</v>
       </c>
       <c r="V192" s="13" t="s">
         <v>205</v>
       </c>
       <c r="W192" s="15" t="s">
-        <v>205</v>
+        <v>1568</v>
       </c>
       <c r="X192" s="15" t="s">
         <v>1569</v>
       </c>
-      <c r="Y192" s="15" t="s">
-        <v>1570</v>
-      </c>
     </row>
     <row r="193">
       <c r="A193" s="11" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B193" s="12" t="s">
         <v>110</v>
@@ -17693,43 +17510,40 @@
         <v>322</v>
       </c>
       <c r="L193" s="35" t="s">
+        <v>1571</v>
+      </c>
+      <c r="M193" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N193" s="13" t="s">
         <v>1572</v>
       </c>
-      <c r="M193" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N193" s="13" t="s">
+      <c r="O193" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P193" s="13" t="s">
         <v>1573</v>
-      </c>
-      <c r="O193" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P193" s="13" t="s">
-        <v>1574</v>
       </c>
       <c r="Q193" s="13"/>
       <c r="R193" s="35" t="s">
+        <v>1574</v>
+      </c>
+      <c r="S193" s="13" t="s">
         <v>1575</v>
       </c>
-      <c r="S193" s="13" t="s">
+      <c r="V193" s="13" t="s">
+        <v>1541</v>
+      </c>
+      <c r="W193" s="15" t="s">
         <v>1576</v>
-      </c>
-      <c r="V193" s="13" t="s">
-        <v>1542</v>
-      </c>
-      <c r="W193" s="15" t="s">
-        <v>1542</v>
       </c>
       <c r="X193" s="15" t="s">
         <v>1577</v>
       </c>
-      <c r="Y193" s="15" t="s">
-        <v>1578</v>
-      </c>
     </row>
     <row r="194">
       <c r="A194" s="11" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="B194" s="12" t="s">
         <v>110</v>
@@ -17747,7 +17561,7 @@
         <v>190</v>
       </c>
       <c r="H194" s="12" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="I194" s="13" t="s">
         <v>57</v>
@@ -17756,29 +17570,29 @@
         <v>437</v>
       </c>
       <c r="L194" s="14" t="s">
+        <v>1580</v>
+      </c>
+      <c r="M194" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N194" s="13" t="s">
         <v>1581</v>
-      </c>
-      <c r="M194" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N194" s="13" t="s">
-        <v>1582</v>
       </c>
       <c r="O194" s="13"/>
       <c r="P194" s="13" t="s">
+        <v>1582</v>
+      </c>
+      <c r="Q194" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R194" s="13" t="s">
         <v>1583</v>
       </c>
-      <c r="Q194" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R194" s="13" t="s">
+      <c r="S194" s="13" t="s">
         <v>1584</v>
       </c>
-      <c r="S194" s="13" t="s">
+      <c r="V194" s="13" t="s">
         <v>1585</v>
-      </c>
-      <c r="V194" s="13" t="s">
-        <v>1586</v>
       </c>
       <c r="W194" s="15" t="s">
         <v>1586</v>
@@ -17786,13 +17600,10 @@
       <c r="X194" s="15" t="s">
         <v>1587</v>
       </c>
-      <c r="Y194" s="15" t="s">
-        <v>1588</v>
-      </c>
     </row>
     <row r="195">
       <c r="A195" s="13" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B195" s="12" t="s">
         <v>110</v>
@@ -17817,45 +17628,42 @@
         <v>322</v>
       </c>
       <c r="L195" s="14" t="s">
+        <v>1589</v>
+      </c>
+      <c r="M195" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N195" s="13" t="s">
         <v>1590</v>
       </c>
-      <c r="M195" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N195" s="13" t="s">
+      <c r="O195" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P195" s="13" t="s">
         <v>1591</v>
       </c>
-      <c r="O195" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P195" s="13" t="s">
+      <c r="Q195" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R195" s="13" t="s">
         <v>1592</v>
       </c>
-      <c r="Q195" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R195" s="13" t="s">
+      <c r="S195" s="13" t="s">
         <v>1593</v>
-      </c>
-      <c r="S195" s="13" t="s">
-        <v>1594</v>
       </c>
       <c r="V195" s="13" t="s">
         <v>274</v>
       </c>
       <c r="W195" s="15" t="s">
-        <v>274</v>
+        <v>1594</v>
       </c>
       <c r="X195" s="15" t="s">
         <v>1595</v>
       </c>
-      <c r="Y195" s="15" t="s">
-        <v>1596</v>
-      </c>
     </row>
     <row r="196">
       <c r="A196" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="B196" s="12" t="s">
         <v>110</v>
@@ -17864,7 +17672,7 @@
         <v>179</v>
       </c>
       <c r="D196" s="12" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="E196" s="13" t="s">
         <v>22</v>
@@ -17873,7 +17681,7 @@
         <v>190</v>
       </c>
       <c r="H196" s="12" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="I196" s="13" t="s">
         <v>57</v>
@@ -17882,43 +17690,40 @@
         <v>1101</v>
       </c>
       <c r="L196" s="35" t="s">
+        <v>1599</v>
+      </c>
+      <c r="M196" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N196" s="13" t="s">
         <v>1600</v>
       </c>
-      <c r="M196" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N196" s="13" t="s">
+      <c r="O196" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P196" s="13" t="s">
         <v>1601</v>
       </c>
-      <c r="O196" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P196" s="13" t="s">
+      <c r="Q196" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R196" s="13" t="s">
         <v>1602</v>
       </c>
-      <c r="Q196" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R196" s="13" t="s">
+      <c r="S196" s="13" t="s">
         <v>1603</v>
       </c>
-      <c r="S196" s="13" t="s">
-        <v>1604</v>
-      </c>
       <c r="U196" s="13" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="V196" s="13" t="s">
         <v>626</v>
       </c>
       <c r="W196" s="15" t="s">
-        <v>626</v>
+        <v>1604</v>
       </c>
       <c r="X196" s="15" t="s">
         <v>1605</v>
-      </c>
-      <c r="Y196" s="15" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="197">
@@ -17948,45 +17753,42 @@
         <v>79</v>
       </c>
       <c r="L197" s="35" t="s">
+        <v>1606</v>
+      </c>
+      <c r="M197" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N197" s="13" t="s">
         <v>1607</v>
       </c>
-      <c r="M197" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N197" s="13" t="s">
+      <c r="O197" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P197" s="13" t="s">
         <v>1608</v>
       </c>
-      <c r="O197" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P197" s="13" t="s">
+      <c r="Q197" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R197" s="13" t="s">
         <v>1609</v>
       </c>
-      <c r="Q197" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R197" s="13" t="s">
+      <c r="S197" s="13" t="s">
         <v>1610</v>
-      </c>
-      <c r="S197" s="13" t="s">
-        <v>1611</v>
       </c>
       <c r="V197" s="13" t="s">
         <v>50</v>
       </c>
       <c r="W197" s="15" t="s">
-        <v>50</v>
+        <v>1611</v>
       </c>
       <c r="X197" s="15" t="s">
         <v>1612</v>
       </c>
-      <c r="Y197" s="15" t="s">
-        <v>1613</v>
-      </c>
     </row>
     <row r="198">
       <c r="A198" s="11" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="B198" s="12" t="s">
         <v>110</v>
@@ -18011,72 +17813,111 @@
         <v>217</v>
       </c>
       <c r="L198" s="35" t="s">
+        <v>1614</v>
+      </c>
+      <c r="M198" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N198" s="13" t="s">
         <v>1615</v>
       </c>
-      <c r="M198" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N198" s="13" t="s">
+      <c r="O198" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="P198" s="13" t="s">
         <v>1616</v>
       </c>
-      <c r="O198" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P198" s="13" t="s">
+      <c r="Q198" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R198" s="13" t="s">
         <v>1617</v>
       </c>
-      <c r="Q198" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="R198" s="13" t="s">
+      <c r="S198" s="13" t="s">
         <v>1618</v>
-      </c>
-      <c r="S198" s="13" t="s">
-        <v>1619</v>
       </c>
       <c r="V198" s="13" t="s">
         <v>205</v>
       </c>
       <c r="W198" s="15" t="s">
-        <v>205</v>
+        <v>1619</v>
       </c>
       <c r="X198" s="15" t="s">
         <v>1620</v>
       </c>
-      <c r="Y198" s="15" t="s">
+    </row>
+    <row r="199" ht="15.0" customHeight="1">
+      <c r="A199" s="11" t="s">
         <v>1621</v>
       </c>
-    </row>
-    <row r="199" ht="15.0" customHeight="1">
-      <c r="A199" s="11"/>
-      <c r="B199" s="12"/>
-      <c r="C199" s="12"/>
-      <c r="D199" s="12"/>
-      <c r="H199" s="20"/>
-      <c r="L199" s="35"/>
-    </row>
-    <row r="200">
+      <c r="B199" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C199" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D199" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E199" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G199" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H199" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="I199" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="J199" s="13" t="s">
+        <v>1622</v>
+      </c>
+      <c r="L199" s="35" t="s">
+        <v>1623</v>
+      </c>
+      <c r="M199" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N199" s="13" t="s">
+        <v>1624</v>
+      </c>
+      <c r="P199" s="13" t="s">
+        <v>1625</v>
+      </c>
+      <c r="Q199" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R199" s="13" t="s">
+        <v>1626</v>
+      </c>
+      <c r="S199" s="13" t="s">
+        <v>1014</v>
+      </c>
+      <c r="V199" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="W199" s="49" t="s">
+        <v>1555</v>
+      </c>
+      <c r="X199" s="49" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="11"/>
-      <c r="B200" s="20"/>
-      <c r="C200" s="20"/>
-      <c r="D200" s="20"/>
+      <c r="B200" s="12"/>
+      <c r="C200" s="12"/>
+      <c r="D200" s="12"/>
       <c r="H200" s="20"/>
-      <c r="L200" s="48"/>
-      <c r="M200" s="13"/>
-      <c r="O200" s="13"/>
-      <c r="Q200" s="13"/>
+      <c r="L200" s="35"/>
     </row>
     <row r="201">
-      <c r="A201" s="50"/>
+      <c r="A201" s="11"/>
       <c r="B201" s="20"/>
       <c r="C201" s="20"/>
-      <c r="D201" s="20">
-        <f t="shared" ref="D201:D203" si="1">COUNTIF(E1:E190, E201)</f>
-        <v>62</v>
-      </c>
-      <c r="E201" s="13" t="s">
-        <v>45</v>
-      </c>
+      <c r="D201" s="20"/>
       <c r="H201" s="20"/>
       <c r="L201" s="48"/>
       <c r="M201" s="13"/>
@@ -18088,23 +17929,17 @@
       <c r="B202" s="20"/>
       <c r="C202" s="20"/>
       <c r="D202" s="20">
-        <f t="shared" si="1"/>
-        <v>79</v>
+        <f t="shared" ref="D202:D204" si="1">COUNTIF(E1:E190, E202)</f>
+        <v>62</v>
       </c>
       <c r="E202" s="13" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H202" s="20"/>
       <c r="L202" s="48"/>
-      <c r="M202" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="O202" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q202" s="13" t="s">
-        <v>9</v>
-      </c>
+      <c r="M202" s="13"/>
+      <c r="O202" s="13"/>
+      <c r="Q202" s="13"/>
     </row>
     <row r="203">
       <c r="A203" s="50"/>
@@ -18112,10 +17947,10 @@
       <c r="C203" s="20"/>
       <c r="D203" s="20">
         <f t="shared" si="1"/>
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="E203" s="13" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H203" s="20"/>
       <c r="L203" s="48"/>
@@ -18123,6 +17958,9 @@
         <v>9</v>
       </c>
       <c r="O203" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q203" s="13" t="s">
         <v>9</v>
       </c>
     </row>
@@ -18130,7 +17968,13 @@
       <c r="A204" s="50"/>
       <c r="B204" s="20"/>
       <c r="C204" s="20"/>
-      <c r="D204" s="20"/>
+      <c r="D204" s="20">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="E204" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="H204" s="20"/>
       <c r="L204" s="48"/>
       <c r="M204" s="13" t="s">
@@ -18144,13 +17988,7 @@
       <c r="A205" s="50"/>
       <c r="B205" s="20"/>
       <c r="C205" s="20"/>
-      <c r="D205" s="20">
-        <f t="shared" ref="D205:D207" si="2">COUNTIF(G1:G190, E205)</f>
-        <v>70</v>
-      </c>
-      <c r="E205" s="13" t="s">
-        <v>23</v>
-      </c>
+      <c r="D205" s="20"/>
       <c r="H205" s="20"/>
       <c r="L205" s="48"/>
       <c r="M205" s="13" t="s">
@@ -18165,11 +18003,11 @@
       <c r="B206" s="20"/>
       <c r="C206" s="20"/>
       <c r="D206" s="20">
-        <f t="shared" si="2"/>
-        <v>19</v>
+        <f t="shared" ref="D206:D208" si="2">COUNTIF(G1:G190, E206)</f>
+        <v>70</v>
       </c>
       <c r="E206" s="13" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H206" s="20"/>
       <c r="L206" s="48"/>
@@ -18186,10 +18024,10 @@
       <c r="C207" s="20"/>
       <c r="D207" s="20">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E207" s="13" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H207" s="20"/>
       <c r="L207" s="48"/>
@@ -18205,11 +18043,11 @@
       <c r="B208" s="20"/>
       <c r="C208" s="20"/>
       <c r="D208" s="20">
-        <f t="shared" ref="D208:D209" si="3">COUNTIF(G4:G195, E208)</f>
-        <v>25</v>
+        <f t="shared" si="2"/>
+        <v>20</v>
       </c>
       <c r="E208" s="13" t="s">
-        <v>110</v>
+        <v>37</v>
       </c>
       <c r="H208" s="20"/>
       <c r="L208" s="48"/>
@@ -18225,11 +18063,11 @@
       <c r="B209" s="20"/>
       <c r="C209" s="20"/>
       <c r="D209" s="20">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f t="shared" ref="D209:D210" si="3">COUNTIF(G4:G195, E209)</f>
+        <v>25</v>
       </c>
       <c r="E209" s="13" t="s">
-        <v>1214</v>
+        <v>110</v>
       </c>
       <c r="H209" s="20"/>
       <c r="L209" s="48"/>
@@ -18237,9 +18075,6 @@
         <v>9</v>
       </c>
       <c r="O209" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q209" s="13" t="s">
         <v>9</v>
       </c>
     </row>
@@ -18248,11 +18083,11 @@
       <c r="B210" s="20"/>
       <c r="C210" s="20"/>
       <c r="D210" s="20">
-        <f t="shared" ref="D210:D211" si="4">COUNTIF(G6:G202, E210)</f>
-        <v>41</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="E210" s="13" t="s">
-        <v>190</v>
+        <v>1214</v>
       </c>
       <c r="H210" s="20"/>
       <c r="L210" s="48"/>
@@ -18271,11 +18106,11 @@
       <c r="B211" s="20"/>
       <c r="C211" s="20"/>
       <c r="D211" s="20">
-        <f t="shared" si="4"/>
-        <v>11</v>
+        <f t="shared" ref="D211:D212" si="4">COUNTIF(G6:G203, E211)</f>
+        <v>41</v>
       </c>
       <c r="E211" s="13" t="s">
-        <v>750</v>
+        <v>190</v>
       </c>
       <c r="H211" s="20"/>
       <c r="L211" s="48"/>
@@ -18293,7 +18128,13 @@
       <c r="A212" s="50"/>
       <c r="B212" s="20"/>
       <c r="C212" s="20"/>
-      <c r="D212" s="20"/>
+      <c r="D212" s="20">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="E212" s="13" t="s">
+        <v>750</v>
+      </c>
       <c r="H212" s="20"/>
       <c r="L212" s="48"/>
       <c r="M212" s="13" t="s">
@@ -32790,44 +32631,73 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1065">
+      <c r="A1065" s="50"/>
+      <c r="B1065" s="20"/>
+      <c r="C1065" s="20"/>
+      <c r="D1065" s="20"/>
+      <c r="H1065" s="20"/>
+      <c r="L1065" s="48"/>
+      <c r="M1065" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1065" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q1065" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$AG$1064"/>
+  <autoFilter ref="$A$1:$AG$1065"/>
   <mergeCells count="84">
-    <mergeCell ref="Y164:AA164"/>
-    <mergeCell ref="Y165:AA165"/>
-    <mergeCell ref="Y166:AA166"/>
-    <mergeCell ref="Y167:AA167"/>
-    <mergeCell ref="Y168:AA168"/>
-    <mergeCell ref="Y169:AA169"/>
-    <mergeCell ref="Y170:AA170"/>
-    <mergeCell ref="Y171:AA171"/>
-    <mergeCell ref="Y172:AA172"/>
-    <mergeCell ref="Y173:AA173"/>
-    <mergeCell ref="Y174:AA174"/>
-    <mergeCell ref="Y175:AA175"/>
-    <mergeCell ref="Y176:AA176"/>
-    <mergeCell ref="Y177:AA177"/>
-    <mergeCell ref="Y178:AA178"/>
-    <mergeCell ref="Y179:AA179"/>
-    <mergeCell ref="Y180:AA180"/>
-    <mergeCell ref="Y181:AA181"/>
-    <mergeCell ref="Y182:AA182"/>
-    <mergeCell ref="Y183:AA183"/>
-    <mergeCell ref="Y184:AA184"/>
-    <mergeCell ref="Y192:AA192"/>
-    <mergeCell ref="Y193:AA193"/>
-    <mergeCell ref="Y194:AA194"/>
-    <mergeCell ref="Y195:AA195"/>
-    <mergeCell ref="Y196:AA196"/>
-    <mergeCell ref="Y197:AA197"/>
-    <mergeCell ref="Y198:AA198"/>
-    <mergeCell ref="Y185:AA185"/>
-    <mergeCell ref="Y186:AA186"/>
-    <mergeCell ref="Y187:AA187"/>
-    <mergeCell ref="Y188:AA188"/>
-    <mergeCell ref="Y189:AA189"/>
-    <mergeCell ref="Y190:AA190"/>
-    <mergeCell ref="Y191:AA191"/>
+    <mergeCell ref="X189:Z189"/>
+    <mergeCell ref="X190:Z190"/>
+    <mergeCell ref="X180:Z180"/>
+    <mergeCell ref="X181:Z181"/>
+    <mergeCell ref="X182:Z182"/>
+    <mergeCell ref="X183:Z183"/>
+    <mergeCell ref="X184:Z184"/>
+    <mergeCell ref="X192:Z192"/>
+    <mergeCell ref="X193:Z193"/>
+    <mergeCell ref="X191:Z191"/>
+    <mergeCell ref="X143:Z143"/>
+    <mergeCell ref="X144:Z144"/>
+    <mergeCell ref="X159:Z159"/>
+    <mergeCell ref="X160:Z160"/>
+    <mergeCell ref="X161:Z161"/>
+    <mergeCell ref="X162:Z162"/>
+    <mergeCell ref="X41:Y41"/>
+    <mergeCell ref="X42:Y42"/>
+    <mergeCell ref="X43:Y43"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="X45:Y45"/>
+    <mergeCell ref="X164:Z164"/>
+    <mergeCell ref="X165:Z165"/>
+    <mergeCell ref="X163:Z163"/>
+    <mergeCell ref="X129:Y129"/>
+    <mergeCell ref="X130:Y130"/>
+    <mergeCell ref="X131:Y131"/>
+    <mergeCell ref="X132:Y132"/>
+    <mergeCell ref="X133:Y133"/>
+    <mergeCell ref="X134:Y134"/>
+    <mergeCell ref="X135:Y135"/>
+    <mergeCell ref="X136:Y136"/>
+    <mergeCell ref="X137:Y137"/>
+    <mergeCell ref="X138:Y138"/>
+    <mergeCell ref="X139:Y139"/>
+    <mergeCell ref="X140:Y140"/>
+    <mergeCell ref="X141:Y141"/>
+    <mergeCell ref="X142:Y142"/>
+    <mergeCell ref="X157:Z157"/>
+    <mergeCell ref="X158:Z158"/>
+    <mergeCell ref="X150:Z150"/>
+    <mergeCell ref="X151:Z151"/>
+    <mergeCell ref="X152:Z152"/>
+    <mergeCell ref="X153:Z153"/>
+    <mergeCell ref="X154:Z154"/>
+    <mergeCell ref="X155:Z155"/>
+    <mergeCell ref="X156:Z156"/>
     <mergeCell ref="X34:Y34"/>
     <mergeCell ref="X35:Y35"/>
     <mergeCell ref="X36:Y36"/>
@@ -32835,57 +32705,45 @@
     <mergeCell ref="X38:Y38"/>
     <mergeCell ref="X39:Y39"/>
     <mergeCell ref="X40:Y40"/>
-    <mergeCell ref="X41:Y41"/>
-    <mergeCell ref="X42:Y42"/>
-    <mergeCell ref="X43:Y43"/>
-    <mergeCell ref="X44:Y44"/>
-    <mergeCell ref="X45:Y45"/>
-    <mergeCell ref="Y127:Z127"/>
-    <mergeCell ref="Y128:Z128"/>
-    <mergeCell ref="Y129:Z129"/>
-    <mergeCell ref="Y130:Z130"/>
-    <mergeCell ref="Y131:Z131"/>
-    <mergeCell ref="Y132:Z132"/>
-    <mergeCell ref="Y133:Z133"/>
-    <mergeCell ref="Y134:Z134"/>
-    <mergeCell ref="Y135:Z135"/>
-    <mergeCell ref="Y136:Z136"/>
-    <mergeCell ref="Y137:Z137"/>
-    <mergeCell ref="Y138:Z138"/>
-    <mergeCell ref="Y139:Z139"/>
-    <mergeCell ref="Y140:Z140"/>
-    <mergeCell ref="Y141:Z141"/>
-    <mergeCell ref="Y142:Z142"/>
-    <mergeCell ref="Y143:AA143"/>
-    <mergeCell ref="Y144:AA144"/>
-    <mergeCell ref="Y145:AA145"/>
-    <mergeCell ref="Y146:AA146"/>
-    <mergeCell ref="Y147:AA147"/>
-    <mergeCell ref="Y148:AA148"/>
-    <mergeCell ref="Y149:AA149"/>
-    <mergeCell ref="Y150:AA150"/>
-    <mergeCell ref="Y151:AA151"/>
-    <mergeCell ref="Y152:AA152"/>
-    <mergeCell ref="Y153:AA153"/>
-    <mergeCell ref="Y154:AA154"/>
-    <mergeCell ref="Y155:AA155"/>
-    <mergeCell ref="Y156:AA156"/>
-    <mergeCell ref="Y157:AA157"/>
-    <mergeCell ref="Y158:AA158"/>
-    <mergeCell ref="Y159:AA159"/>
-    <mergeCell ref="Y160:AA160"/>
-    <mergeCell ref="Y161:AA161"/>
-    <mergeCell ref="Y162:AA162"/>
-    <mergeCell ref="Y163:AA163"/>
+    <mergeCell ref="X166:Z166"/>
+    <mergeCell ref="X167:Z167"/>
+    <mergeCell ref="X168:Z168"/>
+    <mergeCell ref="X169:Z169"/>
+    <mergeCell ref="X170:Z170"/>
+    <mergeCell ref="X171:Z171"/>
+    <mergeCell ref="X172:Z172"/>
+    <mergeCell ref="X173:Z173"/>
+    <mergeCell ref="X174:Z174"/>
+    <mergeCell ref="X175:Z175"/>
+    <mergeCell ref="X176:Z176"/>
+    <mergeCell ref="X177:Z177"/>
+    <mergeCell ref="X178:Z178"/>
+    <mergeCell ref="X179:Z179"/>
+    <mergeCell ref="X194:Z194"/>
+    <mergeCell ref="X195:Z195"/>
+    <mergeCell ref="X196:Z196"/>
+    <mergeCell ref="X197:Z197"/>
+    <mergeCell ref="X198:Z198"/>
+    <mergeCell ref="X185:Z185"/>
+    <mergeCell ref="X186:Z186"/>
+    <mergeCell ref="X187:Z187"/>
+    <mergeCell ref="X188:Z188"/>
+    <mergeCell ref="X127:Y127"/>
+    <mergeCell ref="X128:Y128"/>
+    <mergeCell ref="X145:Z145"/>
+    <mergeCell ref="X146:Z146"/>
+    <mergeCell ref="X147:Z147"/>
+    <mergeCell ref="X148:Z148"/>
+    <mergeCell ref="X149:Z149"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B7 B9:B23 B25:B32 B34:B45 B47:B198">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B7 B9:B23 B25:B32 B34:B45 B47:B199">
       <formula1>Datas!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E3:E7 E9:E23 E25:E32 E34:E45 E47:E198 E201:E203">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E3:E7 E9:E23 E25:E32 E34:E45 E47:E199 E202:E204">
       <formula1>Datas!$E$2:$E$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G3:G7 G9:G23 G25:G32 G34:G45 G47:G198 E205:E211">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G3:G7 G9:G23 G25:G32 G34:G45 G47:G199 E206:E212">
       <formula1>Datas!$C$2:$C$9</formula1>
     </dataValidation>
   </dataValidations>
@@ -32906,37 +32764,37 @@
   <sheetData>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>1622</v>
+        <v>1627</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>1623</v>
+        <v>1628</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>1624</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="s">
-        <v>1622</v>
+        <v>1627</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1625</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>1628</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="32">
@@ -32965,10 +32823,10 @@
   <sheetData>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>1629</v>
+        <v>1634</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>1630</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="3">
@@ -32976,50 +32834,50 @@
         <v>183</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>1632</v>
+        <v>1637</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>1633</v>
+        <v>1638</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>1634</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="s">
-        <v>1635</v>
+        <v>1640</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1636</v>
+        <v>1641</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>1637</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="7">
       <c r="C7" s="23"/>
       <c r="I7" s="13" t="s">
-        <v>1638</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="8">
       <c r="I8" s="13" t="s">
-        <v>1639</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="9">
       <c r="I9" s="13" t="s">
-        <v>1640</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="10">
       <c r="I10" s="13" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
     </row>
   </sheetData>
@@ -33112,275 +32970,275 @@
   <sheetData>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>1642</v>
+        <v>1647</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>1643</v>
+        <v>1648</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>1644</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="13" t="s">
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>1646</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>1648</v>
+        <v>1653</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>1649</v>
+        <v>1654</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>1650</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1651</v>
+        <v>1656</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>1652</v>
+        <v>1657</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>1653</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>1654</v>
+        <v>1659</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1655</v>
+        <v>1660</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>1656</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1657</v>
+        <v>1662</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>1658</v>
+        <v>1663</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>1659</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>1661</v>
+        <v>1666</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>1662</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1663</v>
+        <v>1668</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>1664</v>
+        <v>1669</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>1665</v>
+        <v>1670</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>1666</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>1667</v>
+        <v>1672</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>1668</v>
+        <v>1673</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>1669</v>
+        <v>1674</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>1670</v>
+        <v>1675</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>1671</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1672</v>
+        <v>1677</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>1673</v>
+        <v>1678</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>1674</v>
+        <v>1679</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>1675</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1676</v>
+        <v>1681</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>1677</v>
+        <v>1682</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>1678</v>
+        <v>1683</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>1679</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1680</v>
+        <v>1685</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>1681</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>1682</v>
+        <v>1687</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15">
       <c r="A15" s="13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1684</v>
+        <v>1689</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>1685</v>
+        <v>1690</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>1686</v>
+        <v>1691</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>1687</v>
+        <v>1692</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1688</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1689</v>
+        <v>1694</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>1687</v>
+        <v>1692</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>1690</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="13" t="s">
-        <v>1691</v>
+        <v>1696</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>1692</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="13" t="s">
-        <v>1693</v>
+        <v>1698</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>1694</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="s">
-        <v>1662</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="13" t="s">
-        <v>1695</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="13" t="s">
-        <v>1696</v>
+        <v>1701</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>1697</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="13" t="s">
-        <v>1698</v>
+        <v>1703</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>1699</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="13" t="s">
-        <v>1700</v>
+        <v>1705</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>1701</v>
+        <v>1706</v>
       </c>
     </row>
   </sheetData>
